--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9686DF3F-74BF-4F2F-B15F-AB9446300D90}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9549ABF6-FFFB-43BC-BD8E-2CF02FAD1F6C}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="267">
   <si>
     <t>Image</t>
   </si>
@@ -468,9 +468,6 @@
     <t>https://pictures.abebooks.com/isbn/9781873200896-us.jpg</t>
   </si>
   <si>
-    <t>~ 160 CHF</t>
-  </si>
-  <si>
     <t>https://www.loveramics.com/cdn/shop/files/C099-19A_C099-78A_6b04fe54-a378-4be5-a3fe-968b39d5537e.png?v=1727169104&amp;width=700</t>
   </si>
   <si>
@@ -780,18 +777,6 @@
     <t>https://www.fantasywelt.de/media/image/product/217055/lg/arkham-horror-the-card-game-chapter-two-core-set-en.jpg</t>
   </si>
   <si>
-    <t>PureRef Business</t>
-  </si>
-  <si>
-    <t>50 USD</t>
-  </si>
-  <si>
-    <t>https://www.pureref.com/download.php</t>
-  </si>
-  <si>
-    <t>https://www.pureref.com/images/PureRef.svg</t>
-  </si>
-  <si>
     <t>Joc Steam: Esoteric Ebb</t>
   </si>
   <si>
@@ -802,6 +787,60 @@
   </si>
   <si>
     <t>https://shared.akamai.steamstatic.com/store_item_assets/steam/apps/2057760/3fc3e737678a0d5db6816609bec2c9c6f2c11a88/header.jpg?t=1776091835</t>
+  </si>
+  <si>
+    <t>Philips OneBlade Pro 360 Face + Body</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/4/2/5/6/2/7/5/6/2/9/0/7/3/7/9/9/4/8/8/01a07c22-c7ed-7cff-b1e6-e1ee88cf1c3e_720.avif</t>
+  </si>
+  <si>
+    <t>https://www.galaxus.ch/en/s6/product/philips-oneblade-pro-360-face-body-trimmers-hair-clippers-45971889</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/-/en/City-Darkness-Revisited-Ian-Lambot/dp/1873200889?crid=3N06HZ45I9RPH&amp;dib=eyJ2IjoiMSJ9.vnzayTWGCn8WrF0EEHbbllG6DwfjwkH5r1PfkEW2aHCxu48ydFTGVAjlbQdd6G--nTYYXQA-7we442-7Ss4gMjf81eqJNj46NB1ekIp6TQZ-XybYXgkQ36JZScYvCDidWBYvtPqQ5uVCD_cx7vjbJaOi2WPtBd2_0KDj3_T_MszB5KfTCA6ysbc2RfMSlTqruhtqBqzucnT0tPlqHMQSH8YfjvRhstpn_2EoAp4fDvw.6zVVpAnacYqjq7_FoBoxi0g4HhMWWIAuFEWJdeVGGcQ&amp;dib_tag=se&amp;keywords=city+of+darkness+girard&amp;qid=1790014582&amp;sprefix=city+of+darkness+girard%2Caps%2C116&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t>City of Darkness Revisited</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/61PJeOyy4LL.jpg</t>
+  </si>
+  <si>
+    <t>89 EUR</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/en-ch/product/wallace-gromit-21371</t>
+  </si>
+  <si>
+    <t>110 CHF</t>
+  </si>
+  <si>
+    <t>https://www.lego.com/cdn/cs/set/assets/bltaaaf5b2a2943fa95/21371_boxprod_v29.png?format=webply&amp;fit=bounds&amp;quality=75&amp;width=800&amp;height=800&amp;dpr=1</t>
+  </si>
+  <si>
+    <t>LEGO® 21371 Wallace &amp; Gromit</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>~ 100 CHF</t>
+  </si>
+  <si>
+    <t>Lanterna - TBD</t>
+  </si>
+  <si>
+    <t>Geanta</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/3/0/5/0/4/0/6/4/0/3/2/9/6/9/5/2/7/8/4/019b149b-1fed-7cdd-9097-e23b3c7c18e8_1000.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/peak-design-everyday-sling-camera-shoulder-bag-6-l-camera-bag-60670840</t>
+  </si>
+  <si>
+    <t>129 CHF</t>
   </si>
 </sst>
 </file>
@@ -836,7 +875,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,12 +885,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -869,12 +902,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1197,8 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -1222,211 +1253,166 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>142</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="B3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="B4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>249</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" t="s">
+        <v>251</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" t="s">
-        <v>194</v>
-      </c>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="D12" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="E13" t="s">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1442,872 +1428,1032 @@
       <c r="D14" s="3">
         <v>160</v>
       </c>
+      <c r="E14" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
+        <v>204</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" t="s">
-        <v>219</v>
+        <v>206</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D16" s="3">
         <v>40</v>
       </c>
+      <c r="E16" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" t="s">
-        <v>220</v>
+        <v>203</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
-      </c>
-      <c r="D17" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>181</v>
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
+      </c>
+      <c r="B19" t="s">
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="3">
+        <v>147</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B20" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>204</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" t="s">
-        <v>205</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>97</v>
-      </c>
       <c r="E32" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C36" t="s">
+        <v>230</v>
+      </c>
+      <c r="D36" t="s">
+        <v>232</v>
+      </c>
+      <c r="E36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>239</v>
+      </c>
+      <c r="B37" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" t="s">
+        <v>237</v>
+      </c>
+      <c r="D37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C38" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="3">
+        <v>40</v>
+      </c>
+      <c r="E38" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>103</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B39" t="s">
         <v>106</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C39" t="s">
         <v>104</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D39" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>121</v>
-      </c>
-      <c r="C38" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E38" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" t="s">
-        <v>128</v>
-      </c>
-      <c r="C39" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" t="s">
-        <v>130</v>
-      </c>
       <c r="E39" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
+        <v>4</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
-      </c>
-      <c r="B41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" t="s">
-        <v>135</v>
+        <v>7</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>144</v>
-      </c>
-      <c r="B42" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" t="s">
-        <v>146</v>
+        <v>53</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" t="s">
-        <v>148</v>
+        <v>24</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="E44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
-      </c>
-      <c r="C45" t="s">
-        <v>151</v>
+        <v>19</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
-      </c>
-      <c r="C46" t="s">
-        <v>155</v>
+        <v>26</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>173</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>225</v>
+      <c r="A48" t="s">
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>222</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="E48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>203</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
+      </c>
+      <c r="B50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" t="s">
+        <v>196</v>
       </c>
       <c r="E50" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>166</v>
-      </c>
-      <c r="B52" t="s">
-        <v>167</v>
+        <v>179</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="E52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C53" t="s">
-        <v>93</v>
+        <v>43</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="C54" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="E54" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E55" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>186</v>
-      </c>
-      <c r="C56" t="s">
-        <v>187</v>
-      </c>
-      <c r="D56" s="3">
-        <v>40</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="D59" t="s">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>229</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
-        <v>228</v>
+        <v>79</v>
+      </c>
+      <c r="E60" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="D61" t="s">
-        <v>233</v>
+        <v>78</v>
+      </c>
+      <c r="E61" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
-        <v>235</v>
+        <v>84</v>
+      </c>
+      <c r="E63" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>240</v>
+        <v>98</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>238</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="E64" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>245</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="E65" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="D66" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="E66" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>113</v>
       </c>
       <c r="D67" t="s">
-        <v>252</v>
+        <v>114</v>
+      </c>
+      <c r="E67" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" t="s">
+        <v>119</v>
+      </c>
+      <c r="D69" t="s">
+        <v>122</v>
+      </c>
+      <c r="E69" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D72" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E59" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-    <filterColumn colId="4">
-      <filters blank="1">
-        <filter val="GAP"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D8">
-    <sortCondition ref="D3:D8"/>
+  <autoFilter ref="A1:E22" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A40:D46">
+    <sortCondition ref="D41:D46"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
-    <hyperlink ref="B43" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
-    <hyperlink ref="C21" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
-    <hyperlink ref="C24" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
-    <hyperlink ref="B18" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
-    <hyperlink ref="C50" r:id="rId9" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
+    <hyperlink ref="B41" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
+    <hyperlink ref="B43" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
+    <hyperlink ref="C44" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
+    <hyperlink ref="B44" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
+    <hyperlink ref="C53" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
+    <hyperlink ref="C56" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
+    <hyperlink ref="B52" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
+    <hyperlink ref="B7" r:id="rId9" xr:uid="{75C97756-3FC9-464A-9CCA-2E74F6AB3330}"/>
+    <hyperlink ref="C27" r:id="rId10" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 

--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="14_{7808EC8F-397C-4CFC-A707-B713EAAA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9549ABF6-FFFB-43BC-BD8E-2CF02FAD1F6C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DF940B-4250-4726-B137-D98961237568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="274">
   <si>
     <t>Image</t>
   </si>
@@ -159,15 +159,6 @@
     <t>Set of 2 Beans Dosing Trays</t>
   </si>
   <si>
-    <t>https://www.loveramics.com/collections/brewers-glass-jug-servers/products/brewers-glass-jug</t>
-  </si>
-  <si>
-    <t>500ml Tall Glass Jug with Lid</t>
-  </si>
-  <si>
-    <t>21.95 EUR</t>
-  </si>
-  <si>
     <t>https://www.loveramics.com/collections/diner-mugs/products/bond-250ml-starsky-mug-granite-carmel-gunpowder</t>
   </si>
   <si>
@@ -468,9 +459,6 @@
     <t>https://pictures.abebooks.com/isbn/9781873200896-us.jpg</t>
   </si>
   <si>
-    <t>https://www.loveramics.com/cdn/shop/files/C099-19A_C099-78A_6b04fe54-a378-4be5-a3fe-968b39d5537e.png?v=1727169104&amp;width=700</t>
-  </si>
-  <si>
     <t>Pulp Fiction [4K Ultra HD]</t>
   </si>
   <si>
@@ -663,12 +651,6 @@
     <t>High and Low 4K Blu-ray</t>
   </si>
   <si>
-    <t>Flow 4K Blu-ray</t>
-  </si>
-  <si>
-    <t>The Princess Bride 4K Blu-ray</t>
-  </si>
-  <si>
     <t>https://www.wog.ch/nas/cover_large/p5/p5_ghostofyotei.jpg</t>
   </si>
   <si>
@@ -687,21 +669,9 @@
     <t>https://www.amazon.com/gp/product/B0FDJ6ZV5S?smid=ATVPDKIKX0DER&amp;psc=1</t>
   </si>
   <si>
-    <t>https://www.amazon.com/gp/product/B0C879DRHW?smid=ATVPDKIKX0DER&amp;psc=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/gp/product/B0DYJKJQPF?smid=ATVPDKIKX0DER&amp;psc=1</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81sB3vLwdCL._SL1500_.jpg</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/81M6shZoulL._SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71IHLi5qPLL._SL1500_.jpg</t>
-  </si>
-  <si>
     <t>SKIP (skip: hide from display) / Y (reserved: show faded out) / GAP (formatting gap)</t>
   </si>
   <si>
@@ -828,9 +798,6 @@
     <t>~ 100 CHF</t>
   </si>
   <si>
-    <t>Lanterna - TBD</t>
-  </si>
-  <si>
     <t>Geanta</t>
   </si>
   <si>
@@ -841,6 +808,61 @@
   </si>
   <si>
     <t>129 CHF</t>
+  </si>
+  <si>
+    <t>https://www.firefly-outdoor.com/cdn/shop/files/20260812081928_2346_26.jpg?v=1786507457&amp;width=1600</t>
+  </si>
+  <si>
+    <t>https://www.firefly-outdoor.com/collections/ffl-flashlights/products/e04-surge-lume-x1?variant=47472331292886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanterna E04 Surge - Lume X1 (Fossil Grey MAO / FFL5009R 3500K CRI95 3200lms 230m (Rosy) / Samsung 50S 5000mAh 30A 21700 Battery)
+</t>
+  </si>
+  <si>
+    <t>Flow</t>
+  </si>
+  <si>
+    <t>https://www.cede.ch/en/movies/flow-2024-criterion-collection-special-edition-4k-ultra-hd-and-2-blu-rays-19102043?articleGroupId=5</t>
+  </si>
+  <si>
+    <t>54 CHF</t>
+  </si>
+  <si>
+    <t>https://blob.cede.ch/catalog/19102000/19102043_1_92.jpg?v=1</t>
+  </si>
+  <si>
+    <t>The Princess Bride</t>
+  </si>
+  <si>
+    <t>https://blob.cede.ch/catalog/18199000/18199824_1_92.jpg?v=1</t>
+  </si>
+  <si>
+    <t>https://www.cede.ch/en/movies/the-princess-bride-1987-criterion-collection-4k-ultra-hd-and-blu-ray-18199824</t>
+  </si>
+  <si>
+    <t>58 CHF</t>
+  </si>
+  <si>
+    <t>High and Low</t>
+  </si>
+  <si>
+    <t>https://blob.cede.ch/catalog/19102000/19102029_1_92.jpg?v=1</t>
+  </si>
+  <si>
+    <t>https://www.cede.ch/en/movies/high-and-low-1963-b-w-criterion-collection-restored-special-edition-4k-ultra-hd-19102029</t>
+  </si>
+  <si>
+    <t>500ml Optic Glass Jug and 8cm Glass Lid (Match with Tall / Belly / Optic Jug)</t>
+  </si>
+  <si>
+    <t>35 EUR</t>
+  </si>
+  <si>
+    <t>https://eushop.loveramics.com/cdn/shop/files/C099-76A_C099-78A_d75ccbee-7521-48cd-82b3-661392d56e5c.png?v=1755155438&amp;width=1200</t>
+  </si>
+  <si>
+    <t>https://eushop.loveramics.com/products/brewers-glass-jug-optic</t>
   </si>
 </sst>
 </file>
@@ -926,10 +948,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1229,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -1253,1204 +1271,1227 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D3" s="3">
-        <v>40</v>
+        <v>265</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="3">
-        <v>40</v>
+        <v>260</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>262</v>
+        <v>267</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" t="s">
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" t="s">
-        <v>233</v>
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="3">
-        <v>160</v>
+        <v>236</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
       </c>
       <c r="E14" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>203</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>213</v>
+        <v>136</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>205</v>
+        <v>137</v>
+      </c>
+      <c r="D15" s="3">
+        <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="3">
-        <v>40</v>
+        <v>200</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" t="s">
-        <v>106</v>
+        <v>199</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
+        <v>200</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>224</v>
+      <c r="A20" t="s">
+        <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>228</v>
+      <c r="A21" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="C22" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>202</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>201</v>
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" t="s">
-        <v>167</v>
-      </c>
-      <c r="D28" t="s">
-        <v>168</v>
+        <v>198</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="E31" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="3">
-        <v>40</v>
+        <v>87</v>
+      </c>
+      <c r="D32" t="s">
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
+        <v>182</v>
+      </c>
+      <c r="D33" s="3">
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>229</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B37" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C37" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="D37" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="E37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
+      </c>
+      <c r="B38" t="s">
+        <v>228</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
-      </c>
-      <c r="D38" s="3">
-        <v>40</v>
+        <v>227</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" t="s">
-        <v>106</v>
+        <v>202</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>105</v>
+        <v>208</v>
+      </c>
+      <c r="D39" s="3">
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>193</v>
+        <v>37</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D50" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E50" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B51" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="E51" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="B52" t="s">
+        <v>203</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D52" t="s">
-        <v>178</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>175</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" t="s">
+        <v>173</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E56" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="E57" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E59" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E60" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E62" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D63" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E70" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
         <v>125</v>
       </c>
       <c r="C71" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D73" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>139</v>
+      </c>
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" t="s">
+        <v>141</v>
+      </c>
+      <c r="D74" t="s">
+        <v>142</v>
+      </c>
+      <c r="E74" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A40:D46">
-    <sortCondition ref="D41:D46"/>
+  <autoFilter ref="A1:E23" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:D47">
+    <sortCondition ref="D42:D47"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B41" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
-    <hyperlink ref="B43" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
-    <hyperlink ref="C44" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
-    <hyperlink ref="B44" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
-    <hyperlink ref="C53" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
-    <hyperlink ref="C56" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
-    <hyperlink ref="B52" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
+    <hyperlink ref="B42" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
+    <hyperlink ref="B44" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
+    <hyperlink ref="C45" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
+    <hyperlink ref="B45" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
+    <hyperlink ref="C54" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
+    <hyperlink ref="C57" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
+    <hyperlink ref="B53" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
     <hyperlink ref="B7" r:id="rId9" xr:uid="{75C97756-3FC9-464A-9CCA-2E74F6AB3330}"/>
-    <hyperlink ref="C27" r:id="rId10" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
+    <hyperlink ref="C28" r:id="rId10" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>

--- a/wishlist_valentin.xlsx
+++ b/wishlist_valentin.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DF940B-4250-4726-B137-D98961237568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{86DF940B-4250-4726-B137-D98961237568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A159BD8-8829-4FC8-AE18-2A9E22A12C09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Valentin" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Valentin'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="278">
   <si>
     <t>Image</t>
   </si>
@@ -863,6 +863,18 @@
   </si>
   <si>
     <t>https://eushop.loveramics.com/products/brewers-glass-jug-optic</t>
+  </si>
+  <si>
+    <t>Futura Pro 36 - cherry masala</t>
+  </si>
+  <si>
+    <t>166 CHF</t>
+  </si>
+  <si>
+    <t>https://www.galaxus.ch/en/s8/product/deuter-futura-pro-36-36-l-backpacks-61144487</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/6/5/2/4/3/6/9/1/1/0/4/0/4/1/6/1/1/8/4/01a01aa0-0876-7969-8322-c7346ef66e39_720.avif</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
@@ -1373,17 +1385,17 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>249</v>
+      <c r="A9" t="s">
+        <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1401,39 +1413,36 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" t="s">
+      <c r="A11" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" t="s">
-        <v>223</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>250</v>
@@ -1441,16 +1450,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
         <v>250</v>
@@ -1458,16 +1467,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="3">
-        <v>160</v>
+        <v>236</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
       </c>
       <c r="E15" t="s">
         <v>250</v>
@@ -1475,16 +1484,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>207</v>
+        <v>136</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>201</v>
+        <v>137</v>
+      </c>
+      <c r="D16" s="3">
+        <v>160</v>
       </c>
       <c r="E16" t="s">
         <v>250</v>
@@ -1492,16 +1501,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" s="3">
-        <v>40</v>
+        <v>200</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E17" t="s">
         <v>250</v>
@@ -1509,16 +1518,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
+      </c>
+      <c r="D18" s="3">
+        <v>40</v>
       </c>
       <c r="E18" t="s">
         <v>250</v>
@@ -1526,16 +1535,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>103</v>
+        <v>199</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>102</v>
+        <v>200</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="E19" t="s">
         <v>250</v>
@@ -1543,30 +1552,30 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>214</v>
+      <c r="A21" t="s">
+        <v>213</v>
       </c>
       <c r="B21" t="s">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>211</v>
+        <v>143</v>
       </c>
       <c r="D21" t="s">
         <v>111</v>
@@ -1576,17 +1585,17 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>218</v>
+      <c r="A22" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D22" t="s">
-        <v>217</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>250</v>
@@ -1594,16 +1603,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D23" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
         <v>250</v>
@@ -1611,33 +1620,33 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
         <v>190</v>
@@ -1645,16 +1654,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
         <v>190</v>
@@ -1662,16 +1671,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
         <v>190</v>
@@ -1679,16 +1688,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>197</v>
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
       </c>
       <c r="E28" t="s">
         <v>190</v>
@@ -1696,16 +1705,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>161</v>
-      </c>
-      <c r="B29" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" t="s">
-        <v>164</v>
+        <v>198</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="E29" t="s">
         <v>190</v>
@@ -1713,16 +1722,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
         <v>190</v>
@@ -1730,16 +1739,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
         <v>190</v>
@@ -1747,16 +1756,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
         <v>190</v>
@@ -1764,16 +1773,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
-      </c>
-      <c r="D33" s="3">
-        <v>40</v>
+        <v>87</v>
+      </c>
+      <c r="D33" t="s">
+        <v>88</v>
       </c>
       <c r="E33" t="s">
         <v>190</v>
@@ -1781,16 +1790,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" t="s">
-        <v>156</v>
+        <v>182</v>
+      </c>
+      <c r="D34" s="3">
+        <v>40</v>
       </c>
       <c r="E34" t="s">
         <v>190</v>
@@ -1798,16 +1807,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
         <v>190</v>
@@ -1815,16 +1824,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
         <v>190</v>
@@ -1832,16 +1841,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
         <v>190</v>
@@ -1849,16 +1858,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s">
         <v>190</v>
@@ -1866,16 +1875,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>202</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>209</v>
+        <v>229</v>
+      </c>
+      <c r="B39" t="s">
+        <v>228</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="3">
-        <v>40</v>
+        <v>227</v>
+      </c>
+      <c r="D39" t="s">
+        <v>230</v>
       </c>
       <c r="E39" t="s">
         <v>190</v>
@@ -1883,16 +1892,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>100</v>
-      </c>
-      <c r="B40" t="s">
-        <v>103</v>
+        <v>202</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>102</v>
+        <v>208</v>
+      </c>
+      <c r="D40" s="3">
+        <v>40</v>
       </c>
       <c r="E40" t="s">
         <v>190</v>
@@ -1900,16 +1909,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" t="s">
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="E41" t="s">
         <v>190</v>
@@ -1917,16 +1926,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
         <v>190</v>
@@ -1934,16 +1943,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>190</v>
@@ -1951,16 +1960,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E44" t="s">
         <v>190</v>
@@ -1968,16 +1977,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
         <v>190</v>
@@ -1985,16 +1994,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
         <v>190</v>
@@ -2002,16 +2011,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E47" t="s">
         <v>190</v>
@@ -2019,16 +2028,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
         <v>190</v>
@@ -2036,16 +2045,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E49" t="s">
         <v>190</v>
@@ -2053,16 +2062,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="D50" t="s">
-        <v>189</v>
+        <v>37</v>
       </c>
       <c r="E50" t="s">
         <v>190</v>
@@ -2070,16 +2079,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D51" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E51" t="s">
         <v>190</v>
@@ -2087,16 +2096,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B52" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="E52" t="s">
         <v>190</v>
@@ -2104,16 +2113,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>175</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>176</v>
+        <v>205</v>
+      </c>
+      <c r="B53" t="s">
+        <v>203</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>174</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>190</v>
@@ -2121,16 +2130,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>39</v>
+        <v>175</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" t="s">
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s">
         <v>190</v>
@@ -2138,16 +2147,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
         <v>190</v>
@@ -2155,16 +2164,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E56" t="s">
         <v>190</v>
@@ -2172,16 +2181,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
         <v>190</v>
@@ -2189,16 +2198,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="E58" t="s">
         <v>190</v>
@@ -2206,16 +2215,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
         <v>190</v>
@@ -2223,16 +2232,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E60" t="s">
         <v>190</v>
@@ -2240,16 +2249,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E61" t="s">
         <v>190</v>
@@ -2257,16 +2266,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
         <v>190</v>
@@ -2274,16 +2283,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D63" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E63" t="s">
         <v>190</v>
@@ -2291,16 +2300,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E64" t="s">
         <v>190</v>
@@ -2308,16 +2317,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s">
         <v>190</v>
@@ -2325,16 +2334,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E66" t="s">
         <v>190</v>
@@ -2342,16 +2351,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
         <v>190</v>
@@ -2359,16 +2368,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E68" t="s">
         <v>190</v>
@@ -2376,16 +2385,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E69" t="s">
         <v>190</v>
@@ -2393,16 +2402,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D70" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E70" t="s">
         <v>190</v>
@@ -2410,16 +2419,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E71" t="s">
         <v>190</v>
@@ -2427,16 +2436,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E72" t="s">
         <v>190</v>
@@ -2444,16 +2453,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C73" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E73" t="s">
         <v>190</v>
@@ -2461,37 +2470,54 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" t="s">
+        <v>133</v>
+      </c>
+      <c r="E74" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>139</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>140</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>141</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D75" t="s">
         <v>142</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E75" t="s">
         <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:D47">
-    <sortCondition ref="D42:D47"/>
+  <autoFilter ref="A1:E24" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A42:D48">
+    <sortCondition ref="D43:D48"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B42" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
-    <hyperlink ref="B12" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
-    <hyperlink ref="B44" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
-    <hyperlink ref="C45" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
-    <hyperlink ref="B45" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
-    <hyperlink ref="C54" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
-    <hyperlink ref="C57" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
-    <hyperlink ref="B53" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
+    <hyperlink ref="B43" r:id="rId1" xr:uid="{88D7FD61-7495-433B-BB0E-0F6A89ABE74A}"/>
+    <hyperlink ref="B13" r:id="rId2" xr:uid="{63CC93D1-B3B9-4AD9-8A03-C49E71BB178F}"/>
+    <hyperlink ref="B45" r:id="rId3" xr:uid="{BE3001C8-C6F4-4958-8E83-375C8631FFD0}"/>
+    <hyperlink ref="C46" r:id="rId4" xr:uid="{B0629CDA-CE4C-4A68-98F2-514ED65E6764}"/>
+    <hyperlink ref="B46" r:id="rId5" xr:uid="{E8D94EF1-4592-45B9-B8B2-6EE34CDA156B}"/>
+    <hyperlink ref="C55" r:id="rId6" xr:uid="{5F8F8A1D-DECA-423A-B681-8EB6D1C72089}"/>
+    <hyperlink ref="C58" r:id="rId7" xr:uid="{EA0AE655-D84E-4CA0-B64D-234DB4B1F86A}"/>
+    <hyperlink ref="B54" r:id="rId8" xr:uid="{962EF1F7-F1F1-425B-85D9-C19696DDDA8A}"/>
     <hyperlink ref="B7" r:id="rId9" xr:uid="{75C97756-3FC9-464A-9CCA-2E74F6AB3330}"/>
-    <hyperlink ref="C28" r:id="rId10" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
+    <hyperlink ref="C29" r:id="rId10" xr:uid="{9CC374CE-9746-4369-A4C1-2ED078F270F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
